--- a/backend/wp_templates/G/G9 其他非流动金融资产.xlsx
+++ b/backend/wp_templates/G/G9 其他非流动金融资产.xlsx
@@ -14192,7 +14192,7 @@
       </c>
       <c r="K12" s="81"/>
       <c r="L12" s="144">
-        <f>E12+K12</f>
+        <f>J12+K12</f>
         <v>0</v>
       </c>
       <c r="M12" s="81"/>
@@ -14226,7 +14226,7 @@
       </c>
       <c r="X12" s="81"/>
       <c r="Y12" s="144">
-        <f>R12+X12</f>
+        <f>W12+X12</f>
         <v>0</v>
       </c>
       <c r="Z12" s="81"/>
@@ -14258,7 +14258,7 @@
       </c>
       <c r="K13" s="81"/>
       <c r="L13" s="144">
-        <f t="shared" ref="L13:L16" si="5">E13+K13</f>
+        <f t="shared" ref="L13:L16" si="5">J13+K13</f>
         <v>0</v>
       </c>
       <c r="M13" s="81"/>
@@ -14292,7 +14292,7 @@
       </c>
       <c r="X13" s="81"/>
       <c r="Y13" s="144">
-        <f t="shared" ref="Y13:Y16" si="9">R13+X13</f>
+        <f t="shared" ref="Y13:Y16" si="9">W13+X13</f>
         <v>0</v>
       </c>
       <c r="Z13" s="81"/>
@@ -14660,7 +14660,7 @@
       </c>
       <c r="K19" s="81"/>
       <c r="L19" s="144">
-        <f t="shared" ref="L19:L23" si="15">E19+K19</f>
+        <f t="shared" ref="L19:L23" si="15">J19+K19</f>
         <v>0</v>
       </c>
       <c r="M19" s="81"/>
@@ -14694,7 +14694,7 @@
       </c>
       <c r="X19" s="81"/>
       <c r="Y19" s="144">
-        <f t="shared" ref="Y19:Y23" si="19">R19+X19</f>
+        <f t="shared" ref="Y19:Y23" si="19">W19+X19</f>
         <v>0</v>
       </c>
       <c r="Z19" s="81"/>
@@ -15126,7 +15126,7 @@
       </c>
       <c r="K26" s="81"/>
       <c r="L26" s="144">
-        <f t="shared" ref="L26:L28" si="25">E26+K26</f>
+        <f t="shared" ref="L26:L28" si="25">J26+K26</f>
         <v>0</v>
       </c>
       <c r="M26" s="81"/>
@@ -15160,7 +15160,7 @@
       </c>
       <c r="X26" s="81"/>
       <c r="Y26" s="144">
-        <f t="shared" ref="Y26:Y28" si="27">R26+X26</f>
+        <f t="shared" ref="Y26:Y28" si="27">W26+X26</f>
         <v>0</v>
       </c>
       <c r="Z26" s="81"/>
